--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_02_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_02_20_Cau.xlsx
@@ -815,7 +815,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn signal thực sự so output với evidence hoặc authority.</t>
+          <t>Đánh giá rủi ro hallucination khi dữ liệu lớn đòi hỏi phối hợp đa tầng: (a) Kiểm tra đối chiếu tự động giữa thực thể/claim với nguồn truy xuất (groundedness check), (b) lấy mẫu định kỳ chấm bằng LLM judge có version cố định, (c) chuyển chuyên gia con người hoặc hệ thống hồ sơ gốc (system-of-record) rà soát các trường hợp bất đồng có rủi ro cao.</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Tool success rate, Timeout rate.</t>
+          <t>Báo cáo số liệu công cụ chính xác: Tỷ lệ thành công là 80/100 = 80%; các tỷ lệ lỗi (timeout, invalid schema, provider failure) và tỷ lệ lặp lại (loop rate) phải được tính toán dựa trên đúng mẫu số tương ứng.</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đối chiếu các lựa chọn với: Correlation, Provider/model/version.</t>
+          <t>Tập trường tối thiểu cần thiết để debug độ trễ và chi phí theo model/prompt mà không làm rò rỉ PII: Mã định danh tương quan, phiên bản prompt/model, số lượng token, thời gian xử lý và kết quả thực thi.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_02_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_13_Full_137_Cau/Day_13_Ngan_Hang_Phan_02_20_Cau.xlsx
@@ -624,10 +624,28 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra At-least-one probability, Repeated turn.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra At-least-one probability, Repeated turn.</t>
+- 1.0đ: Thiết lập đúng công thức xác suất phần bù cho chuỗi độc lập: $1 - (1 - p)^n$.
+- 1.0đ: Tính toán số học chính xác: $1 - 0.98^5 \approx 0.0961$ (hoặc $9.61\%$).
+- 1.0đ: Phân tích được ý nghĩa kỹ thuật: rủi ro tail tăng vọt từ 2% lên gần 10% khi kết hợp tuần tự.
+- 1.0đ: Nêu rõ các giới hạn của mô hình (vi phạm giả định độc lập, tương quan nghẽn hạ tầng, thiếu cơ chế hedge/retry).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính xác suất ít nhất một tail event:
+- Số bước tuần tự độc lập: $n = 5$.
+- Xác suất xảy ra tail event ở mỗi bước đơn lẻ: $p = 0.02$ ($2\%$).
+- Xác suất một bước KHÔNG gặp tail event: $q = 1 - p = 1 - 0.02 = 0.98$ ($98\%$).
+- Vì 5 bước độc lập, xác suất cả 5 bước đều KHÔNG gặp tail event là:
+  $$P(\text{không có tail}) = q^5 = 0.98^5 = 0.9039207968 \approx 90.39\%$$
+- Xác suất workflow gặp ÍT NHẤT MỘT tail event là biến cố đối:
+  $$P(\ge 1 \text{ tail}) = 1 - P(\text{không có tail}) = 1 - 0.90392 \approx 0.09608 \approx \mathbf{9.61\%}$$
+- Nhận xét: Dù mỗi bước riêng lẻ chỉ có 2% rủi ro trễ đuôi, nhưng qua chuỗi 5 bước, rủi ro toàn bộ workflow bị trễ đuôi tăng lên gần gấp 5 lần (gần 10%).
+2. Giới hạn của mô hình toán học:
+- **Giả định độc lập không thực tế (Correlation of Failures)**: Trong thực tế, các bước trong workflow thường phụ thuộc cùng hạ tầng (ví dụ cùng network, cùng cluster database). Nếu bước 1 bị trễ do quá tải, các bước sau có xác suất cao bị trễ theo (correlated tail latency), làm phá vỡ giả định độc lập.
+- **Cộng dồn độ trễ phi tuyến (Non-additive compounding)**: Tail event ở bước trước có thể gây timeout hoặc dồn hàng đợi ở bước sau, khiến độ trễ tổng thể tăng theo cấp số nhân thay vì chỉ là xác suất rời rạc.
+- **Thiếu mô hình hóa Mitigation**: Mô hình lý thuyết chưa phản ánh các kỹ thuật công nghệ như hedged requests (gửi song song để lấy kết quả nhanh nhất) hoặc circuit breaker giúp cắt đứt hiệu ứng đuôi trễ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Hiện tượng Tail Latency Compounding (sự tích lũy độ trễ đuôi) được phân tích kinh điển bởi Jeff Dean trong bài báo 'The Tail at Scale'. Khi một kiến trúc phân tán gồm nhiều bước hoặc fan-out nhiều vi dịch vụ tuần tự, xác suất tổng thể gặp sự cố trễ sẽ tăng lũy thừa theo công thức $1 - (1-p)^n$. Điều này giải thích vì sao dù mọi service con đều cam kết SLA P99 rất cao, toàn bộ hệ thống phối hợp (orchestration pipeline) vẫn thường xuyên bị chậm nếu không có kỹ thuật kiểm soát tail chủ động.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Jeffrey Dean &amp; Luiz André Barroso: 'The Tail at Scale' (CACM 2013, https://cacm.acm.org/magazines/2013/2/160173-the-tail-at-scale/fulltext)</t>
         </is>
       </c>
     </row>
@@ -758,10 +776,28 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Automated heuristic, Model judge.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Automated heuristic, Model judge.</t>
+- 1.0đ: Thiết kế Tầng 1 (Rule-based/Presidio/NER) tối ưu tốc độ và chặn rò rỉ PII tức thì với chi phí cực thấp.
+- 1.0đ: Thiết kế Tầng 2 (Small NLI/evaluator model) để phát hiện factual error y khoa với độ trễ thấp và chi phí vừa phải.
+- 1.0đ: Thiết kế Tầng 3 (Frontier Judge / Human Expert audit) cho bằng chứng chuẩn mực cao trên dữ liệu mẫu chọn lọc.
+- 1.0đ: Phân tích được sự phối hợp giữa các tầng thành một thể thống nhất (tốc độ vs bằng chứng vs chi phí).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Signal Stack phân tầng (Pyramid) theo Tốc độ, Sức mạnh Bằng chứng (Evidence Strength) và Chi phí (Cost):
+1. **Tầng 1: Heuristic / Deterministic Rule-based Guardrail (Tốc độ: &lt;10ms, Bằng chứng: Tuyệt đối cho Pattern, Chi phí: Gần bằng 0)**:
+- Mục tiêu: Chặn đứng rò rỉ PII (Personally Identifiable Information) ngay lập tức.
+- Công cụ: Sử dụng Regex, checksums (số CMND/CCCD, thẻ tín dụng), và Microsoft Presidio / RoBERTa-NER on-device.
+- Hành động: Chạy inline ngay trước khi trả kết quả ra ngoài; nếu phát hiện PII, tự động mask hoặc chặn phát hành, phát cảnh báo khẩn PagerDuty.
+2. **Tầng 2: Asynchronous Small Evaluator / NLI Model (Tốc độ: 100-300ms, Bằng chứng: Cao về logic, Chi phí: Thấp/Vừa)**:
+- Mục tiêu: Phát hiện sai lệch sự thật y khoa (Medical Factual Consistency / Contradiction).
+- Công cụ: Chạy mô hình chuyên dụng nhỏ (DeBERTa-v3 cross-encoder hoặc specialized NLI model) kiểm tra từng câu khẳng định trong bản tóm tắt đối chiếu với bệnh án gốc.
+- Hành động: Gán cờ `medical_contradiction_flag` nếu điểm mâu thuẫn &gt; 0.7; kích hoạt fallback về bản tóm tắt mẫu an toàn.
+3. **Tầng 3: Frontier LLM-as-a-Judge &amp; Human Medical Expert Audit (Tốc độ: Vài giây đến vài giờ, Bằng chứng: Toàn diện/Chuẩn mực vàng, Chi phí: Rất cao)**:
+- Mục tiêu: Đánh giá độ chính xác tổng thể, phát hiện lỗi lâm sàng tinh vi và rủi ro điều trị.
+- Công cụ: Lấy mẫu có chủ đích (stratified sample 1-5% ca có độ tự tin thấp hoặc ca bệnh nặng) gửi cho mô hình Frontier kèm rubric y khoa chi tiết và bác sĩ chuyên môn rà soát.
+- Hành động: Đưa vào golden benchmark hồi quy, dùng để hiệu chỉnh lại các bộ lọc ở Tầng 1 và Tầng 2.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Kim tự tháp Tín hiệu Giám sát (Signal Pyramid): Không thể dùng một công cụ duy nhất cho mọi bài toán kiểm định. Đối với các rủi ro có cấu trúc rõ ràng như rò rỉ PII, các bộ lọc quy tắc (deterministic rules) nhanh và rẻ phải đứng ở cửa ngõ. Đối với các lỗi ngữ nghĩa phức tạp như sai lệch sự thật y khoa (factual errors), cần kết hợp giữa mô hình NLI kiểm tra mâu thuẫn tức thời và quy trình chuyên gia con người (human-in-the-loop) kiểm tra mẫu để cân đối hoàn hảo giữa an toàn bệnh nhân, độ trễ hệ thống và ngân sách.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Microsoft Presidio Documentation (https://microsoft.github.io/presidio/) &amp; Google Cloud AI Adoption Framework - Governance and Safety</t>
         </is>
       </c>
     </row>
@@ -846,10 +882,27 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Groundedness, Entity verification.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Groundedness, Entity verification.</t>
+- 1.0đ: Thiết kế chiến lược lấy mẫu phân tầng thông minh (chia tỷ lệ cho rủi ro cao, retrieval thấp, và ngẫu nhiên).
+- 1.0đ: Xây dựng tín hiệu Groundedness/Faithfulness qua phân rã mệnh đề (claim-level verification).
+- 1.0đ: Xây dựng tín hiệu đối chiếu Thực thể / Số liệu và kiểm tra tính xác thực của Citation.
+- 1.0đ: Thiết lập quy trình tổng hợp chỉ số, ngưỡng cảnh báo và hành động vận hành khi phát hiện vi phạm.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế cơ chế kiểm tra Hallucination đa tín hiệu trên dữ liệu mẫu (1% của 100k = 1.000 requests/ngày):
+1. **Chiến lược lấy mẫu phân tầng (Stratified Sampling)**:
+- Không lấy mẫu ngẫu nhiên thuần túy (uniform random). Phân bổ ngân sách 1.000 ca như sau:
+  + 400 ca (40%): Lấy từ nhóm 'rủi ro cao' (câu trả lời dài trên 500 token, câu hỏi chứa thực thể lạ, hoặc user có hành vi copy/regenerate).
+  + 300 ca (30%): Lấy từ các ca có độ tương đồng ngữ nghĩa giữa câu hỏi và context truy vấn ở mức thấp (retrieval score &lt; 0.7).
+  + 300 ca (30%): Lấy mẫu ngẫu nhiên đồng đều trên toàn bộ traffic còn lại để giữ tính đại diện thống kê.
+2. **Hệ thống tín hiệu kết hợp (Multi-signal Verification)**:
+- **Tín hiệu 1 - Groundedness / Faithfulness Check**: Sử dụng mô hình LLM-as-a-Judge nhỏ trích xuất các claims (mệnh đề khẳng định) từ câu trả lời và đối soát 1-1 với reference text của policy để tính tỷ lệ mệnh đề được chứng minh.
+- **Tín hiệu 2 - Entity &amp; Numerical Verification**: Sử dụng trích xuất thực thể để kiểm tra xem mọi con số (khoản tiền, phần trăm, mốc thời gian) và tên văn bản luật trong output có xuất hiện trong reference text hay không.
+- **Tín hiệu 3 - Citation Consistency Check**: Kiểm tra các đoạn trích dẫn (citations) do model gắn có trỏ đúng vào đoạn trích thực tế trong tài liệu chính sách hay không.
+3. **Hành động và Cảnh báo vận hành (Operational Action)**:
+- Tổng hợp thành chỉ số hàng ngày `daily_groundedness_rate`. Nếu tỷ lệ hallucination trong mẫu phân tầng vượt quá 3%, kích hoạt alert xem xét lại chất lượng dữ liệu corpus và hiệu chỉnh prompt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Với lưu lượng lớn (100k req/ngày) và ngân sách hạn hẹp (1%), phương pháp lấy mẫu phân tầng theo tín hiệu rủi ro (Stratified Risk-based Sampling) giúp tối đa hóa khả năng phát hiện lỗi so với lấy mẫu ngẫu nhiên đơn thuần. Đồng thời, việc kết hợp đa tín hiệu (groundedness ngữ nghĩa, thực thể số học, và tính chuẩn xác của trích dẫn) giúp triệt tiêu điểm mù của từng phương pháp đánh giá riêng lẻ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Ragas: Automated Evaluation of Retrieval Augmented Generation (https://docs.ragas.io) &amp; TruLens Groundedness Evaluation</t>
         </is>
       </c>
     </row>
@@ -928,10 +981,29 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Tool success rate, Timeout rate.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Tool success rate, Timeout rate.</t>
+- 1.0đ: Phân định rành mạch giữa Logical Call (ý định nghiệp vụ) và Attempt (số lần thử kỹ thuật).
+- 1.0đ: Định nghĩa chuẩn xác điều kiện nhận diện Request Loop (lặp tham số/không tiến triển) kèm metric theo dõi.
+- 1.0đ: Thiết lập hợp đồng đo lường độ trễ phân tầng (logical latency vs attempt latency).
+- 1.0đ: Đưa ra cơ chế circuit breaker và fallback cụ thể để ngắt vòng lặp tự động.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hợp đồng Chỉ số Tool Call phân định rõ Logical Call, Attempt, và Loop:
+1. **Phân định khái niệm &amp; Metric Contract**:
+- **Logical Call (Lời gọi cấp nghiệp vụ)**: Đại diện cho một ý định duy nhất của Agent nhằm thực hiện một hành động (ví dụ: `action_id = 'query_order_123'`).
+  + Metric: `agent_tool_logical_calls_total{tool_name, status='success|failed'}`.
+- **Attempt (Số lần thử kỹ thuật)**: Mỗi lần thực hiện HTTP request hoặc RPC cụ thể tới tool, bao gồm cả lần đầu và các lần retry khi gặp lỗi tạm thời.
+  + Metric: `agent_tool_attempts_total{tool_name, attempt_number, status_code}`.
+  + Tỷ lệ retry kỹ thuật: `tool_retry_ratio = (attempts_total - logical_calls_total) / logical_calls_total`.
+- **Request Loop (Vòng lặp bất thường)**: Tình trạng Agent bị kẹt, gọi đi gọi lại cùng một tool với cùng bộ tham số (hoặc tham số tương đương) nhiều hơn ngưỡng cho phép ($N \ge 3$) mà không tạo ra tiến triển mới trong suy luận.
+  + Metric: `agent_tool_loop_detected_total{tool_name, agent_id}`.
+2. **Outcome &amp; Latency Contract**:
+- `tool_logical_latency_seconds`: Thời gian từ lúc agent quyết định gọi tool đến khi nhận kết quả cuối cùng (bao gồm toàn bộ các đợt retry).
+- `tool_attempt_latency_seconds`: Thời gian phản hồi của riêng từng attempt đơn lẻ.
+3. **Cơ chế kiểm soát Loop (Guardrail Action)**:
+- Khi phát hiện `attempt_count &gt; 3` trên cùng một logical action hoặc hàm băm `hash(tool_name, args)` lặp lại 3 lần liên tiếp, hệ thống ngắt chuỗi ngay lập tức (circuit break), ghi log error `TOOL_DEADLOCK_LOOP` và trả fallback message cho người dùng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiến trúc Agent, việc không phân tách giữa Logical Call và Attempt sẽ làm sai lệch hoàn toàn bức tranh vận hành: một tác vụ có thể ghi nhận 1 logical call thành công nhưng thực chất đã ngầm tiêu tốn 5 attempts với chi phí và độ trễ khổng lồ. Hơn nữa, nếu không định nghĩa rõ ràng chữ ký của một 'vòng lặp vô tận' (loop detection contract), agent có thể tiêu cạn ngân sách token và tài nguyên hệ thống.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Semantic Conventions for AI Agent Tools (https://opentelemetry.io/docs/specs/semconv/gen-ai/) &amp; LangChain Agent Callback Handler</t>
         </is>
       </c>
     </row>
@@ -1010,10 +1082,28 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Empty-result rate, Retrieval latency.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Empty-result rate, Retrieval latency.</t>
+- 1.0đ: Định nghĩa chuẩn xác các chỉ số Availability (empty-result rate, success rate, latency) và chỉ rõ cạm bẫy của nó.
+- 1.0đ: Thiết lập các chỉ số Quality ngữ nghĩa độc lập (Context Relevance, MRR@k, semantic similarity threshold).
+- 1.0đ: Phân tích cơ chế đánh tráo bản chất giữa việc luôn có kết quả (availability) với việc kết quả có giá trị (quality).
+- 1.0đ: Đưa ra quy tắc kết hợp hai chiều (dual-gate rule) bắt buộc cả hai tiêu chí đều phải đạt ngưỡng trước khi release.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Hệ thống Metric Retrieval phân lập hoàn toàn Tính sẵn sàng (Availability) và Chất lượng (Quality):
+1. **Availability Metrics (Tính sẵn sàng kỹ thuật - Không đánh tráo với chất lượng)**:
+- `retrieval_empty_result_rate`: Tỷ lệ các truy vấn trả về 0 chunks (`len(chunks) == 0`).
+- `retrieval_success_http_rate`: Tỷ lệ các truy vấn vector database không gặp lỗi kết nối (HTTP 200/gRPC OK).
+- `retrieval_latency_seconds` (P50, P95): Thời gian phản hồi của vector index.
+  *Cảnh báo*: Khi corpus mở rộng, `empty_result_rate` giảm có thể chỉ vì hệ thống luôn tìm thấy một đoạn văn bản bất kỳ có độ tương đồng yếu, không đồng nghĩa thông tin đó hữu ích.
+2. **Quality Metrics (Chất lượng nội dung - Ngăn chặn đánh tráo)**:
+- `context_relevance_score` (Ragas metric): Đo lường tỷ lệ các câu trong chunks thực sự liên quan trực tiếp đến câu hỏi của người dùng (loại bỏ nhiễu).
+- `sampled_semantic_similarity`: Điểm tương đồng cosine/BM25 trung bình của top-k chunks, có đặt ngưỡng sàn (ví dụ: score $\ge 0.75$).
+- `reciprocal_rank_at_k` (MRR@k) &amp; `hit_rate_at_k`: Đo lường vị trí xuất hiện của chunk chính xác đầu tiên trong tập kết quả trả về.
+- `groundedness_with_retrieval`: Tỷ lệ câu trả lời cuối cùng của LLM thực sự sử dụng thông tin từ context đã trích xuất.
+3. **Nguyên tắc Gate Release**:
+- Một bản cập nhật corpus chỉ được chấp thuận (pass gate) khi đồng thời thỏa mãn: `empty_result_rate &lt;= 2%` (Availability) VÀ `context_relevance_score &gt;= 0.8` (Quality). Không bao giờ dùng chỉ số availability để bù trừ cho sự suy giảm quality.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Đây là lỗi thiết kế kinh điển trong hệ thống RAG: đội ngũ kỹ thuật thường lạc quan khi thấy chỉ số kết quả rỗng (empty result) giảm sau khi nạp thêm tài liệu. Tuy nhiên, nếu tài liệu mới đưa vào chứa nhiều nội dung rác (noise/distractors), vector search luôn trả về đủ $k$ chunks (availability tốt) nhưng các chunks đó hoàn toàn không liên quan đến câu hỏi (quality sụp đổ). Do đó, hợp đồng giám sát phải tách riêng tính sẵn sàng và chất lượng ngữ nghĩa thành hai tiêu chí độc lập.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+RAGAS: Evaluation of Retrieval Augmented Generation (https://docs.ragas.io/en/stable/concepts/metrics/context_relevance.html) &amp; Pinecone RAG Evaluation Guide</t>
         </is>
       </c>
     </row>
@@ -1096,10 +1186,33 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Provider failure, Timeout.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Provider failure, Timeout.</t>
+- 1.0đ: Phân biệt rành mạch giữa Triệu chứng bề mặt (degraded answer 200 OK) và Nguyên nhân gốc (guardrail block).
+- 1.0đ: Xây dựng taxonomy phân loại chuẩn xác theo từng lớp (Security Guardrail, Knowledge Retrieval, Agent Orchestration).
+- 1.0đ: Gán đúng Ownership cụ thể cho từng thành phần (Trust &amp; Safety, Data/RAG team, Core Agent team).
+- 1.0đ: Thiết lập phản ứng kỹ thuật chuẩn hóa cho từng lớp lỗi mà không che giấu lỗi dưới mã HTTP 200.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Thiết kế Taxonomy phân loại lỗi Agent Runtime, phân định rõ Triệu chứng (Symptom) và Nguyên nhân gốc (Root Cause):
+1. **Bóc tách Triệu chứng vs Nguyên nhân trong ca sự cố**:
+- **Triệu chứng (Symptom)**: Người dùng nhận được 'câu trả lời suy thoái (degraded answer)' với mã HTTP 200. Đây là lớp biểu hiện bên ngoài, không phải bản chất lỗi.
+- **Nguyên nhân tầng giữa (Proximate Cause)**: Retrieval trả về kết quả rỗng (empty retrieval) do không tìm thấy tài liệu phù hợp.
+- **Nguyên nhân gốc (Root Cause)**: Guardrail chặn truy vấn (Guardrail Block) do nhận diện nhầm hoặc vi phạm chính sách nội dung đầu vào, dẫn đến luồng xử lý bị cắt ngắn và fallback về degraded answer.
+2. **Phân bổ Taxonomy, Owner và Phản ứng chuẩn hóa**:
+- **Lớp 1: Policy / Safety Guardrail Trigger**:
+  + Phân loại: `SECURITY_GUARDRAIL_INTERVENTION`.
+  + Owner: Trust &amp; Safety / AI Governance Team.
+  + Phản ứng: Ghi log audit bảo mật; trả thông báo từ chối minh bạch (transparent refusal) thay vì degraded answer mờ ám.
+- **Lớp 2: Knowledge / Retrieval Failure**:
+  + Phân loại: `KNOWLEDGE_BASE_MISS`.
+  + Owner: RAG &amp; Data Engineering Team.
+  + Phản ứng: Kiểm tra độ bao phủ của index; trả fallback message thông báo chưa có dữ liệu chính xác.
+- **Lớp 3: Agent Orchestration &amp; Degradation Handling**:
+  + Phân loại: `AGENT_DEGRADED_COMPLETION`.
+  + Owner: Core AI Agent Team.
+  + Phản ứng: Gắn thẻ telemetry `is_degraded: true` vào response metadata; không ghi nhận đây là standard HTTP 200 success trong metric chất lượng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong vận hành Agent, lỗi thường xảy ra theo dạng chuỗi phản ứng dây chuyền (cascading failure): Guardrail chặn -&gt; Retrieval rỗng -&gt; Agent fallback -&gt; Trả degraded output với HTTP 200. Nếu chỉ nhìn vào triệu chứng cuối cùng, nhóm kỹ sư sẽ nhầm lẫn đây là lỗi của Model hoặc Agent. Phân loại taxonomy rõ ràng giúp truy tìm đúng điểm đứt gãy ban đầu (root cause) và gán đúng trách nhiệm xử lý (ownership) cho đội ngũ liên quan.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book: Tracking Outages &amp; OWASP Top 10 for Large Language Model Applications (https://owasp.org/www-project-top-10-for-large-language-model-applications/)</t>
         </is>
       </c>
     </row>
@@ -1182,10 +1295,22 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Data drift, Concept drift.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Data drift, Concept drift.</t>
+- 1.0đ: Phân tích và loại trừ Data Drift dựa trên dữ kiện đề bài (input distribution ổn định).
+- 1.0đ: Đánh giá đúng bản chất của Concept Drift và chỉ ra tình trạng chưa có bằng chứng khẳng định.
+- 1.0đ: Xác định chính xác Model / Pipeline Degradation là ứng viên số 1 và giải thích nguyên nhân.
+- 1.0đ: Thiết kế kế hoạch bằng chứng kiểm chứng đối chứng (A/B testing trên golden dataset bất biến và human verification).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân loại các ứng viên Drift (Drift Candidates):
+- **Data Drift (Covariate Shift - Thay đổi phân phối đầu vào $P(X)$)**: Đã bị **LOẠI TRỪ** trong bối cảnh này, vì đề bài nêu rõ 'Input distribution ổn định' (phân phối câu hỏi đầu vào không thay đổi).
+- **Concept Drift (Thay đổi mối quan hệ bản chất $P(Y|X)$)**: Đây là **ỨNG VIÊN CẦN XÁC MINH**, nhưng hiện tại 'chưa có bằng chứng chứng minh mối quan hệ giữa câu hỏi và nhãn chân lý thay đổi' (thế giới thực chưa đổi luật lệ hay chuẩn mực).
+- **Model / Pipeline Degradation Drift (Trôi dạt nội tại mô hình)**: Đây là **ỨNG VIÊN KHẢ DĨ NHẤT (Leading Candidate)**. Vì cùng một tập đầu vào và tài liệu tham chiếu (Input/Reference cố định) nhưng Model v2 lại bị sụt giảm điểm số so với v1, chứng tỏ sự suy giảm bắt nguồn từ chính các thay đổi bên trong Model v2 (ví dụ: quantization, thay đổi system prompt, alignment tuning quá đà gây suy giảm năng lực suy luận, hoặc sampling hyperparameters).
+2. Bằng chứng kiểm chứng xác nhận (Confirmation Evidence Plan):
+- **Kiểm chứng Model Drift nội tại**: Chạy Model v1 và v2 song song (A/B offline eval) trên một Golden Benchmark Dataset cố định đã được kiểm định từ trước với nhiệt độ $T=0$. Nếu điểm của v2 vẫn thấp hơn v1 trên cùng tập test bất biến, khẳng định 100% là do Model Degradation.
+- **Kiểm chứng Concept Drift**: Lấy ngẫu nhiên 50 mẫu mà v2 bị chấm điểm thấp gửi cho chuyên gia con người (human annotators) đánh giá lại đáp án chuẩn $Y$. Nếu chuyên gia xác nhận đáp án chuẩn cũ vẫn đúng, loại trừ hoàn toàn Concept Drift.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Giám sát Drift trong AI đòi hỏi sự phân biệt chặt chẽ giữa 3 khái niệm: Data Drift ($P(X)$ thay đổi), Concept Drift ($P(Y|X)$ thay đổi), và Model Degradation ($P_{\theta}(Y|X)$ thay đổi do trọng số hoặc prompt). Khi phân phối đầu vào $X$ và ngữ cảnh tham chiếu không đổi nhưng điểm số mô hình mới giảm, nguyên nhân trực tiếp nằm ở sự thay đổi hành vi suy luận của mô hình (Model Drift) chứ không phải do người dùng hay thế giới bên ngoài thay đổi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Evidently AI Documentation: Data Drift vs Concept Drift (https://docs.evidentlyai.com) &amp; Chip Huyen: Designing Machine Learning Systems (Chapter 8: Data Distribution Shifts)</t>
         </is>
       </c>
     </row>
@@ -1268,10 +1393,28 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Engineering, Product.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Engineering, Product.</t>
+- 1.0đ: Ánh xạ chuẩn xác quyết định và metrics hành động cho nhóm Engineering (độ tin cậy, độ trễ, lỗi).
+- 1.0đ: Ánh xạ chuẩn xác quyết định và metrics hành động cho nhóm Product (tỷ lệ hoàn thành tác vụ, phản hồi người dùng, chất lượng).
+- 1.0đ: Ánh xạ chuẩn xác quyết định và metrics hành động cho nhóm Finance (chi phí trên mỗi tác vụ thành công, biên lợi nhuận, token spend).
+- 1.0đ: Chỉ ra đích danh ít nhất một Vanity Metric cụ thể và lập luận thuyết phục vì sao phải loại bỏ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Ánh xạ Quyết định của từng Stakeholder sang Metric tương ứng:
+- **Engineering (Kỹ thuật hạ tầng &amp; Vận hành)**:
+  + Quyết định: 'Hệ thống có ổn định, tin cậy và đáp ứng SLA kỹ thuật không? Khi nào cần can thiệp on-call?'
+  + Metrics hành động: `P95/P99 latency`, `HTTP 5xx error rate`, `tool_call_failure_rate`, `model_timeout_count`, `circuit_breaker_trips`.
+- **Product (Sản phẩm &amp; Trải nghiệm người dùng)**:
+  + Quyết định: 'Tính năng có thực sự giải quyết được bài toán của người dùng không? Tính năng nào cần cải tiến prompt hay workflow?'
+  + Metrics hành động: `task_completion_rate`, `user_retention_rate`, `regenerate_rate`, `thumbs_up_down_ratio`, `quality_faithfulness_score`.
+- **Finance (Tài chính &amp; Hiệu quả kinh doanh)**:
+  + Quyết định: 'Chi phí vận hành có bền vững không? Đơn giá trên mỗi tác vụ hoàn thành có bảo đảm biên lợi nhuận (unit economics) không?'
+  + Metrics hành động: `cost_per_successful_session_usd`, `total_token_spend_per_feature`, `cache_hit_cost_savings`, `gross_margin_per_tenant`.
+2. Nhận diện và Loại bỏ Vanity Metric (Chỉ số ảo):
+- **Loại bỏ**: `total_prompts_processed` (Tổng số prompt đã xử lý) hoặc `total_model_tokens_generated` (Tổng số token đã sinh ra).
+- **Lý do**: Đây là các chỉ số ảo vì số lượng prompt hoặc token tăng vọt có thể do agent bị kẹt trong vòng lặp vô tận (infinite retry loop) hoặc câu trả lời dài dòng vô ích (verbosity bias). Chỉ số này tăng làm Engineering tốn tải và Finance tốn tiền nhưng Product lại thất bại nếu người dùng không đạt được mục tiêu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc thiết kế Dashboard cho nhiều đối tượng (Stakeholder-centric Dashboard Design): Mỗi nhóm người dùng có một không gian quyết định riêng biệt. Kỹ thuật cần dữ liệu về độ tin cậy và hiệu năng để gỡ lỗi; Sản phẩm cần dữ liệu về mức độ hoàn thành nhiệm vụ và sự hài lòng; Tài chính cần dữ liệu về hiệu quả chi phí đơn vị (unit economics). Cần loại bỏ triệt để các 'vanity metrics' - những con số tạo ảo giác tăng trưởng nhưng không gắn liền với giá trị thực hoặc có thể tăng ngay cả khi hệ thống gặp lỗi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Workbook: Practical Alerting &amp; FinOps Foundation: FinOps Framework for Cloud &amp; AI (https://www.finops.org/framework/)</t>
         </is>
       </c>
     </row>
@@ -1350,10 +1493,44 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Typed JSON event, Required core field.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Typed JSON event, Required core field.</t>
+- 1.0đ: Thiết kế được schema rõ ràng (JSON schema hoặc OpenTelemetry specification) với các trường bắt buộc chuẩn.
+- 1.0đ: Chuẩn hóa triệt để đơn vị thời gian (quy về duration_ms nhất quán, loại bỏ xung đột giây/ms).
+- 1.0đ: Chuẩn hóa trường error thành object có cấu trúc `{code, message}`, loại bỏ việc dùng string tùy tiện.
+- 1.0đ: Nêu rõ cơ chế validation contract ở tầng ingestion pipeline (dead-letter-queue, telemetry error metrics).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Schema Chuẩn hóa cho Structured Event (JSON Schema / OpenTelemetry Format):
+```json
+{
+  "$schema": "http://json-schema.org/draft-07/schema#",
+  "type": "object",
+  "required": ["timestamp_iso", "trace_id", "span_id", "service_name", "duration_ms", "status"],
+  "properties": {
+    "timestamp_iso": { "type": "string", "format": "date-time" },
+    "trace_id": { "type": "string", "pattern": "^[a-f0-9]{32}$" },
+    "span_id": { "type": "string", "pattern": "^[a-f0-9]{16}$" },
+    "service_name": { "type": "string" },
+    "duration_ms": { "type": "number", "minimum": 0, "description": "Thời gian thực thi chuẩn hóa theo milliseconds (ms)" },
+    "status": { "type": "string", "enum": ["OK", "ERROR"] },
+    "error": {
+      "type": ["object", "null"],
+      "required": ["code", "message"],
+      "properties": {
+        "code": { "type": "string" },
+        "message": { "type": "string" },
+        "stack_trace": { "type": "string" }
+      }
+    }
+  }
+}
+```
+2. Validation Contract &amp; Cơ chế Thực thi (Ingestion &amp; Pipeline Governance):
+- **Đơn vị thời gian thống nhất**: Tuyệt đối chuẩn hóa `duration_ms` là số thực (float) tính theo mili-giây. Cấm sử dụng trường `latency` tự do không rõ đơn vị.
+- **Cấu trúc trường Error nhất quán**: Trường `error` bắt buộc phải là một `object` có cấu trúc chuẩn `{code, message}` khi `status == 'ERROR'`, và bằng `null` khi `status == 'OK'`. Cấm phát thải error dưới dạng chuỗi string thuần túy.
+- **Cơ chế Pipeline Enforcement**: Tại OpenTelemetry Collector hoặc Ingestion Gateway, áp dụng validation filter: các event không hợp lệ (sai schema) sẽ bị định tuyến vào `dead-letter-queue` (DLQ) để sửa lỗi và tăng metric `telemetry_schema_validation_errors_total` nhằm cảnh báo ngay cho team phụ trách service.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sự bất đồng nhất trong telemetry (ví dụ một bên bắn giây, một bên bắn mili-giây; lỗi lúc là string lúc là object) là nguyên nhân hàng đầu làm tê liệt các dashboard giám sát và các câu lệnh cảnh báo tự động. Một Structured Event Schema có hợp đồng thực thi (Schema Validation Contract) bảo đảm mọi service đều tuân thủ định dạng chuẩn trước khi dữ liệu được ghi vào kho lưu trữ (Elasticsearch/Loki/ClickHouse).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Specification: Logs Data Model (https://opentelemetry.io/docs/specs/otel/logs/data-model/) &amp; JSON Schema Standard</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1609,37 @@
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Correlation, Provider/model/version.
-Phân tích theo nguyên lý thiết kế: Bắt đầu từ observable outcome rồi lần lượt kiểm tra Correlation, Provider/model/version.</t>
+- 1.0đ: Chọn đầy đủ các trường phục vụ Debug kỹ thuật (model, version, attempt, finish_reason, tool_names).
+- 1.0đ: Chọn đầy đủ các trường phục vụ Quản lý Chi phí (prompt/completion tokens, cached tokens, estimated cost).
+- 1.0đ: Chọn đầy đủ các trường phục vụ Chất lượng lấy mẫu (eval_score, metric_name, evaluation tags).
+- 1.0đ: Thể hiện rõ chiến lược tối thiểu hóa nội dung (loại bỏ raw text, chỉ giữ hash/length để bảo mật).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn trường Telemetry phục vụ Debug / Cost / Quality nhưng Tối thiểu hóa Nội dung (Minimizing Content):
+- **Nhóm trường phục vụ Định danh &amp; Liên kết (Correlation &amp; Tracing)**:
+  + `trace_id` &amp; `span_id`: Liên kết toàn bộ hành trình phân tán.
+  + `session_id` &amp; `user_id_hash`: Định danh phiên làm việc và người dùng đã băm an toàn.
+  + `request_id`: Mã duy nhất của lượt gọi LLM.
+- **Nhóm trường phục vụ Phân tích Kỹ thuật &amp; Debug (Execution &amp; Debug)**:
+  + `provider`: Nhà cung cấp mô hình (e.g., `openai`, `anthropic`, `local-vllm`).
+  + `model_name` &amp; `model_version`: Tên mô hình chính xác (e.g., `gpt-4o-2024-08-06`).
+  + `temperature` &amp; `seed`: Tham số sinh để tái lập hành vi khi cần debug.
+  + `attempt_number` / `retry_count`: Số lần thử lại của lời gọi này.
+  + `finish_reason`: Lý do kết thúc (e.g., `stop`, `length`, `tool_calls`, `content_filter`).
+  + `tool_call_names`: Danh sách tên các công cụ được model kích hoạt (chỉ ghi tên tool, không ghi full args).
+- **Nhóm trường phục vụ Quản lý Chi phí (FinOps &amp; Cost)**:
+  + `prompt_tokens` &amp; `completion_tokens` &amp; `total_tokens`: Số lượng token đầu vào và đầu ra.
+  + `cached_tokens`: Số lượng token đọc từ prompt cache (nếu có).
+  + `estimated_cost_usd`: Chi phí tạm tính dựa trên bảng giá model.
+- **Nhóm trường phục vụ Đánh giá Chất lượng (Sampled Quality)**:
+  + `sampled_eval_score`: Điểm đánh giá chất lượng (nếu request nằm trong mẫu 1-5% eval).
+  + `eval_metric_name`: Tên tiêu chí đánh giá (e.g., `faithfulness`, `relevance`).
+2. Chiến lược Tối thiểu hóa Nội dung (Content Minimization Policy):
+- **LOẠI BỎ (Omit)**: Toàn bộ raw prompt text và raw response text trong telemetry mặc định để bảo vệ bí mật dữ liệu và tiết kiệm băng thông.
+- **THAY THẾ (Substitute)**: Chỉ lưu trữ `prompt_sha256_hash` và `response_length_chars` để phục vụ đối soát khi có khiếu nại.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Thu thập telemetry cho các lời gọi LLM cần tuân thủ nghiêm ngặt nguyên tắc tối thiểu hóa dữ liệu (Data Minimization). Việc lưu toàn bộ chuỗi văn bản (raw prompt/completion) không chỉ gây bùng nổ chi phí lưu trữ mà còn vi phạm các quy định bảo mật dữ liệu (GDPR, HIPAA, SOC2). Bằng cách chỉ lưu các trường metadata có cấu trúc (token counts, hashes, latency, status, finish reasons), hệ thống vẫn hoàn toàn đáp ứng được nhu cầu debug, tính chi phí và đo lường chất lượng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Semantic Conventions for Generative AI (https://opentelemetry.io/docs/specs/semconv/gen-ai/gen-ai-spans/) &amp; ISO/IEC 27701 Privacy Information Management</t>
         </is>
       </c>
     </row>
